--- a/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Accessibility Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Accessibility Tests.xlsx
@@ -145,10 +145,8 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -157,7 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -438,87 +436,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
       <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="G2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Accessibility Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Accessibility Tests.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -27,9 +27,6 @@
     <t>Test Case Title</t>
   </si>
   <si>
-    <t>Test Case Type</t>
-  </si>
-  <si>
     <t>Preconditions</t>
   </si>
   <si>
@@ -48,13 +45,145 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
+    <t>TC-ACC-1</t>
+  </si>
+  <si>
+    <t>Pictures Naming</t>
+  </si>
+  <si>
+    <t>Status (Mobile)</t>
+  </si>
+  <si>
+    <t>1. Enter the Amazon web page</t>
+  </si>
+  <si>
+    <t>1. Check the pictures from Amazon main page</t>
+  </si>
+  <si>
+    <t>2. Verify several products</t>
+  </si>
+  <si>
+    <t>3. For each product also check the "Full View"</t>
+  </si>
+  <si>
+    <t>Verification for namings and titles for all pictures</t>
+  </si>
+  <si>
+    <t>All pictures have name, category or a description of the product on image</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>TC-ACC-2</t>
+  </si>
+  <si>
+    <t>Color Contrast</t>
+  </si>
+  <si>
+    <t>Verification for color contrast ratio for products</t>
+  </si>
+  <si>
+    <t>3. Check the items with color of a background</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All pictures have a different (contrast) background color </t>
+  </si>
+  <si>
+    <t>The white color on products not from main page have white background</t>
+  </si>
+  <si>
+    <t>TC-ACC-3</t>
+  </si>
+  <si>
+    <t>Physical Disability</t>
+  </si>
+  <si>
+    <t>1. Try to manage basic actions only with mouse</t>
+  </si>
+  <si>
+    <t>2. Try to manage basic actions only with keyboard</t>
+  </si>
+  <si>
+    <t>3. Verify the same on different pages of items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic features as writing, chosing and changing the properties have to be doable only by mouse or keyboard </t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Only keyboard interactions are not available (only scrolling the page up and down)</t>
+  </si>
+  <si>
+    <t>Verification if the website can be managed somehow using only keyboard, touchpad or mouse</t>
+  </si>
+  <si>
+    <t>TC-ACC-4</t>
+  </si>
+  <si>
+    <t>Literacy Verification</t>
+  </si>
+  <si>
+    <t>Verification if the text on website is easy to read and understand</t>
+  </si>
+  <si>
+    <t>2. Check the text from several products</t>
+  </si>
+  <si>
+    <t>3. Check the text from some additional functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All text is easy to read and understand for anyone </t>
+  </si>
+  <si>
+    <t>The most important information is writen properly, but several addition info is not easy to read and understand</t>
+  </si>
+  <si>
+    <t>TC-ACC-5</t>
+  </si>
+  <si>
+    <t>Proper Headings</t>
+  </si>
+  <si>
+    <t>TC-ACC-6</t>
+  </si>
+  <si>
+    <t>1. Check the text from main page</t>
+  </si>
+  <si>
+    <t>1. Check the headings from main page</t>
+  </si>
+  <si>
+    <t>2. Check the headings from several products</t>
+  </si>
+  <si>
+    <t>3. Check the headings from some additional functions</t>
+  </si>
+  <si>
+    <t>All headings are setuped properly (heading 1 &lt; heading 2 &lt; heading 3 &lt; …)</t>
+  </si>
+  <si>
+    <t>Cognitive Understanding</t>
+  </si>
+  <si>
+    <t>Verification if the text, buttons, images and stuff is located properly and is easy to understand</t>
+  </si>
+  <si>
+    <t>1. Check the main page</t>
+  </si>
+  <si>
+    <t>2. Check several products</t>
+  </si>
+  <si>
+    <t>3. Check some additional functions</t>
+  </si>
+  <si>
+    <t>Everything on page is located according to best practices and is comfortable to work with</t>
+  </si>
+  <si>
+    <t>Some additional features and informations are not so easy to find</t>
   </si>
 </sst>
 </file>
@@ -142,20 +271,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -436,17 +591,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="42.5546875" customWidth="1"/>
+    <col min="5" max="5" width="44.88671875" customWidth="1"/>
+    <col min="6" max="6" width="37.109375" customWidth="1"/>
+    <col min="7" max="7" width="7.5546875" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
@@ -472,80 +628,396 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="C2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" s="3"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="2" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="10"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="D5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="10"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="14"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="48">
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G8:G10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="G11:G13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="F8:F10"/>
     <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
     <mergeCell ref="G2:G4"/>
-    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="F2:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Accessibility Tests.xlsx
+++ b/E-Commerce Web/Amazon/Test Suites/Non-Functional Testing Suite/Accessibility Tests.xlsx
@@ -190,12 +190,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -273,23 +282,28 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -300,17 +314,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -606,367 +615,367 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="4" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="7" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="4" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="7" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="4" t="s">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="7" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="11"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="4" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="10"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="7" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="11"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="8"/>
+      <c r="I14" s="9"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="4" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="12" t="s">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="10"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="4" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="9"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="10"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="7" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="10"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -1020,5 +1029,6 @@
     <mergeCell ref="F2:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>